--- a/Excel/SteedConfig.xlsx
+++ b/Excel/SteedConfig.xlsx
@@ -161,14 +161,14 @@
     <font>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="微软雅黑"/>
+      <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="微软雅黑"/>
+      <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1106,8 +1106,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:J33"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
+  <dimension ref="C3:J18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="5" width="9" style="1"/>
     <col min="6" max="6" width="17.125" style="1" customWidth="1"/>
@@ -1117,7 +1117,7 @@
     <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" s="1" customFormat="1" ht="13.5" spans="3:10">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1143,7 +1143,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="13.5" spans="3:10">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C4" s="2" t="s">
         <v>8</v>
       </c>
@@ -1169,7 +1169,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="13.5" spans="3:10">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C5" s="2" t="s">
         <v>10</v>
       </c>
@@ -1195,7 +1195,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="3:10">
+    <row r="6" customHeight="1" spans="3:10">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1221,7 +1221,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="3:10">
+    <row r="7" customHeight="1" spans="3:10">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1247,7 +1247,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="3:10">
+    <row r="8" customHeight="1" spans="3:10">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1273,7 +1273,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="3:10">
+    <row r="9" customHeight="1" spans="3:10">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1299,7 +1299,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="3:10">
+    <row r="10" customHeight="1" spans="3:10">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1325,7 +1325,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="3:10">
+    <row r="11" customHeight="1" spans="3:10">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1351,7 +1351,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="3:10">
+    <row r="12" customHeight="1" spans="3:10">
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -1377,7 +1377,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="3:10">
+    <row r="13" customHeight="1" spans="3:10">
       <c r="C13" s="1">
         <v>8</v>
       </c>
@@ -1403,7 +1403,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="3:10">
+    <row r="14" customHeight="1" spans="3:10">
       <c r="C14" s="1">
         <v>9</v>
       </c>
@@ -1429,7 +1429,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="3:10">
+    <row r="15" customHeight="1" spans="3:10">
       <c r="C15" s="1">
         <v>10</v>
       </c>
@@ -1455,7 +1455,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="3:10">
+    <row r="16" customHeight="1" spans="3:10">
       <c r="C16" s="1">
         <v>11</v>
       </c>
@@ -1481,7 +1481,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="3:10">
+    <row r="17" customHeight="1" spans="3:10">
       <c r="C17" s="1">
         <v>12</v>
       </c>
@@ -1507,7 +1507,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="3:10">
+    <row r="18" customHeight="1" spans="3:10">
       <c r="C18" s="1">
         <v>13</v>
       </c>
@@ -1533,7 +1533,6 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" s="1" customFormat="1" ht="81" customHeight="1"/>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="J3:J5 C3:E5" errorStyle="warning">

--- a/Excel/SteedConfig.xlsx
+++ b/Excel/SteedConfig.xlsx
@@ -131,10 +131,10 @@
     <t>闪避</t>
   </si>
   <si>
+    <t>命中</t>
+  </si>
+  <si>
     <t>破韧倍率</t>
-  </si>
-  <si>
-    <t>命中</t>
   </si>
   <si>
     <t>增伤倍率</t>
@@ -316,12 +316,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1463,10 +1463,10 @@
         <v>1</v>
       </c>
       <c r="E16" s="1">
-        <v>2013</v>
+        <v>32</v>
       </c>
       <c r="F16" s="1">
-        <v>5</v>
+        <v>0.2</v>
       </c>
       <c r="G16" s="1">
         <v>7</v>
@@ -1489,10 +1489,10 @@
         <v>1</v>
       </c>
       <c r="E17" s="1">
-        <v>32</v>
+        <v>2013</v>
       </c>
       <c r="F17" s="1">
-        <v>0.2</v>
+        <v>5</v>
       </c>
       <c r="G17" s="1">
         <v>8</v>
